--- a/output/yearly_population_iteration_81_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_81_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7461</v>
+        <v>6230</v>
       </c>
       <c r="C2" t="n">
-        <v>8573</v>
+        <v>7325</v>
       </c>
       <c r="D2" t="n">
-        <v>26183</v>
+        <v>26899</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4416</v>
+        <v>4076</v>
       </c>
       <c r="C3" t="n">
-        <v>5734</v>
+        <v>4859</v>
       </c>
       <c r="D3" t="n">
-        <v>16011</v>
+        <v>17761</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3090</v>
+        <v>3070</v>
       </c>
       <c r="C4" t="n">
-        <v>6525</v>
+        <v>4281</v>
       </c>
       <c r="D4" t="n">
-        <v>7991</v>
+        <v>7364</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2015</v>
+        <v>1998</v>
       </c>
       <c r="C5" t="n">
-        <v>5295</v>
+        <v>3908</v>
       </c>
       <c r="D5" t="n">
-        <v>3156</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1236</v>
+        <v>1217</v>
       </c>
       <c r="C6" t="n">
-        <v>4022</v>
+        <v>2672</v>
       </c>
       <c r="D6" t="n">
-        <v>1258</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="C7" t="n">
-        <v>2559</v>
+        <v>1750</v>
       </c>
       <c r="D7" t="n">
-        <v>667</v>
+        <v>640</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C8" t="n">
-        <v>1199</v>
+        <v>861</v>
       </c>
       <c r="D8" t="n">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C9" t="n">
-        <v>438</v>
+        <v>373</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8274</v>
+        <v>10142</v>
       </c>
       <c r="C2" t="n">
-        <v>6744</v>
+        <v>12204</v>
       </c>
       <c r="D2" t="n">
-        <v>24437</v>
+        <v>25182</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4600</v>
+        <v>4107</v>
       </c>
       <c r="C3" t="n">
-        <v>6127</v>
+        <v>5262</v>
       </c>
       <c r="D3" t="n">
-        <v>16262</v>
+        <v>17810</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3088</v>
+        <v>3027</v>
       </c>
       <c r="C4" t="n">
-        <v>5977</v>
+        <v>4428</v>
       </c>
       <c r="D4" t="n">
-        <v>8979</v>
+        <v>8836</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2165</v>
+        <v>2172</v>
       </c>
       <c r="C5" t="n">
-        <v>5716</v>
+        <v>4002</v>
       </c>
       <c r="D5" t="n">
-        <v>3726</v>
+        <v>3154</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1412</v>
+        <v>1417</v>
       </c>
       <c r="C6" t="n">
-        <v>4471</v>
+        <v>3177</v>
       </c>
       <c r="D6" t="n">
-        <v>1514</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>765</v>
+        <v>784</v>
       </c>
       <c r="C7" t="n">
-        <v>3135</v>
+        <v>2164</v>
       </c>
       <c r="D7" t="n">
-        <v>734</v>
+        <v>688</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="C8" t="n">
-        <v>1744</v>
+        <v>1235</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C9" t="n">
-        <v>724</v>
+        <v>578</v>
       </c>
       <c r="D9" t="n">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C10" t="n">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1307,7 +1307,7 @@
         <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10573</v>
+        <v>10297</v>
       </c>
       <c r="C2" t="n">
-        <v>11343</v>
+        <v>13466</v>
       </c>
       <c r="D2" t="n">
-        <v>31896</v>
+        <v>29533</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4864</v>
+        <v>5252</v>
       </c>
       <c r="C3" t="n">
-        <v>5677</v>
+        <v>7218</v>
       </c>
       <c r="D3" t="n">
-        <v>16162</v>
+        <v>17585</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3108</v>
+        <v>2954</v>
       </c>
       <c r="C4" t="n">
-        <v>5913</v>
+        <v>4704</v>
       </c>
       <c r="D4" t="n">
-        <v>9598</v>
+        <v>9945</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2234</v>
+        <v>2238</v>
       </c>
       <c r="C5" t="n">
-        <v>5642</v>
+        <v>4060</v>
       </c>
       <c r="D5" t="n">
-        <v>4318</v>
+        <v>3846</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1560</v>
+        <v>1573</v>
       </c>
       <c r="C6" t="n">
-        <v>4856</v>
+        <v>3457</v>
       </c>
       <c r="D6" t="n">
-        <v>1755</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>899</v>
+        <v>943</v>
       </c>
       <c r="C7" t="n">
-        <v>3600</v>
+        <v>2580</v>
       </c>
       <c r="D7" t="n">
-        <v>825</v>
+        <v>753</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="C8" t="n">
-        <v>2247</v>
+        <v>1586</v>
       </c>
       <c r="D8" t="n">
-        <v>477</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="C9" t="n">
-        <v>1066</v>
+        <v>823</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>438</v>
+        <v>389</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1598,10 +1598,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9669</v>
+        <v>9367</v>
       </c>
       <c r="C2" t="n">
-        <v>8076</v>
+        <v>9156</v>
       </c>
       <c r="D2" t="n">
-        <v>26447</v>
+        <v>24301</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5590</v>
+        <v>5872</v>
       </c>
       <c r="C3" t="n">
-        <v>9059</v>
+        <v>10441</v>
       </c>
       <c r="D3" t="n">
-        <v>17625</v>
+        <v>19261</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2064</v>
+        <v>2067</v>
       </c>
       <c r="C4" t="n">
-        <v>8481</v>
+        <v>6516</v>
       </c>
       <c r="D4" t="n">
-        <v>9199</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1441</v>
+        <v>1453</v>
       </c>
       <c r="C5" t="n">
-        <v>4758</v>
+        <v>3387</v>
       </c>
       <c r="D5" t="n">
-        <v>2839</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>830</v>
+        <v>871</v>
       </c>
       <c r="C6" t="n">
-        <v>3528</v>
+        <v>2528</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>737</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="C7" t="n">
-        <v>2202</v>
+        <v>1554</v>
       </c>
       <c r="D7" t="n">
-        <v>467</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="C8" t="n">
-        <v>1044</v>
+        <v>806</v>
       </c>
       <c r="D8" t="n">
-        <v>316</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>429</v>
+        <v>381</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
         <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1895,10 +1895,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5738</v>
+        <v>5529</v>
       </c>
       <c r="C2" t="n">
-        <v>3757</v>
+        <v>3907</v>
       </c>
       <c r="D2" t="n">
-        <v>18344</v>
+        <v>16767</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6177</v>
+        <v>6299</v>
       </c>
       <c r="C3" t="n">
-        <v>7861</v>
+        <v>9021</v>
       </c>
       <c r="D3" t="n">
-        <v>17767</v>
+        <v>18837</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2878</v>
+        <v>3021</v>
       </c>
       <c r="C4" t="n">
-        <v>8885</v>
+        <v>8376</v>
       </c>
       <c r="D4" t="n">
-        <v>10309</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1589</v>
+        <v>1608</v>
       </c>
       <c r="C5" t="n">
-        <v>6317</v>
+        <v>4770</v>
       </c>
       <c r="D5" t="n">
-        <v>3539</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>959</v>
+        <v>1021</v>
       </c>
       <c r="C6" t="n">
-        <v>4100</v>
+        <v>2954</v>
       </c>
       <c r="D6" t="n">
-        <v>997</v>
+        <v>921</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>360</v>
+        <v>392</v>
       </c>
       <c r="C7" t="n">
-        <v>2720</v>
+        <v>1957</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>1357</v>
+        <v>1051</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="D9" t="n">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
         <v>97</v>
@@ -2192,10 +2192,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5447</v>
+        <v>6077</v>
       </c>
       <c r="C2" t="n">
-        <v>7383</v>
+        <v>5630</v>
       </c>
       <c r="D2" t="n">
-        <v>14111</v>
+        <v>16395</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5046</v>
+        <v>5068</v>
       </c>
       <c r="C3" t="n">
-        <v>5321</v>
+        <v>5868</v>
       </c>
       <c r="D3" t="n">
-        <v>16822</v>
+        <v>17423</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3597</v>
+        <v>3770</v>
       </c>
       <c r="C4" t="n">
-        <v>8303</v>
+        <v>8517</v>
       </c>
       <c r="D4" t="n">
-        <v>11141</v>
+        <v>11622</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1876</v>
+        <v>1954</v>
       </c>
       <c r="C5" t="n">
-        <v>7319</v>
+        <v>6367</v>
       </c>
       <c r="D5" t="n">
-        <v>4372</v>
+        <v>4339</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1119</v>
+        <v>1166</v>
       </c>
       <c r="C6" t="n">
-        <v>4998</v>
+        <v>3773</v>
       </c>
       <c r="D6" t="n">
-        <v>1349</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>508</v>
+        <v>568</v>
       </c>
       <c r="C7" t="n">
-        <v>3313</v>
+        <v>2405</v>
       </c>
       <c r="D7" t="n">
-        <v>578</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="C8" t="n">
-        <v>1890</v>
+        <v>1424</v>
       </c>
       <c r="D8" t="n">
-        <v>343</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>774</v>
+        <v>664</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
         <v>302</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
         <v>63</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3315</v>
+        <v>3614</v>
       </c>
       <c r="C2" t="n">
-        <v>3600</v>
+        <v>2628</v>
       </c>
       <c r="D2" t="n">
-        <v>9862</v>
+        <v>11488</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5002</v>
+        <v>5123</v>
       </c>
       <c r="C3" t="n">
-        <v>5836</v>
+        <v>5609</v>
       </c>
       <c r="D3" t="n">
-        <v>16324</v>
+        <v>16925</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3918</v>
+        <v>4177</v>
       </c>
       <c r="C4" t="n">
-        <v>8091</v>
+        <v>8292</v>
       </c>
       <c r="D4" t="n">
-        <v>11857</v>
+        <v>12369</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1951</v>
+        <v>2047</v>
       </c>
       <c r="C5" t="n">
-        <v>8721</v>
+        <v>7790</v>
       </c>
       <c r="D5" t="n">
-        <v>4485</v>
+        <v>4593</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>903</v>
+        <v>998</v>
       </c>
       <c r="C6" t="n">
-        <v>5853</v>
+        <v>4572</v>
       </c>
       <c r="D6" t="n">
-        <v>1304</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="C7" t="n">
-        <v>3425</v>
+        <v>2565</v>
       </c>
       <c r="D7" t="n">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>1295</v>
+        <v>1083</v>
       </c>
       <c r="D8" t="n">
-        <v>367</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
         <v>295</v>
       </c>
       <c r="D9" t="n">
-        <v>278</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4097</v>
+        <v>4143</v>
       </c>
       <c r="C2" t="n">
-        <v>10475</v>
+        <v>5441</v>
       </c>
       <c r="D2" t="n">
-        <v>14096</v>
+        <v>13139</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3719</v>
+        <v>3847</v>
       </c>
       <c r="C3" t="n">
-        <v>4351</v>
+        <v>3797</v>
       </c>
       <c r="D3" t="n">
-        <v>14426</v>
+        <v>15210</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3780</v>
+        <v>3979</v>
       </c>
       <c r="C4" t="n">
-        <v>6905</v>
+        <v>6857</v>
       </c>
       <c r="D4" t="n">
-        <v>12182</v>
+        <v>12692</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2396</v>
+        <v>2567</v>
       </c>
       <c r="C5" t="n">
-        <v>8351</v>
+        <v>7929</v>
       </c>
       <c r="D5" t="n">
-        <v>5410</v>
+        <v>5573</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1166</v>
+        <v>1278</v>
       </c>
       <c r="C6" t="n">
-        <v>7015</v>
+        <v>5934</v>
       </c>
       <c r="D6" t="n">
-        <v>1727</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>381</v>
       </c>
       <c r="C7" t="n">
-        <v>4418</v>
+        <v>3420</v>
       </c>
       <c r="D7" t="n">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>2050</v>
+        <v>1641</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>607</v>
+        <v>558</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2918</v>
+        <v>3084</v>
       </c>
       <c r="C2" t="n">
-        <v>5858</v>
+        <v>3414</v>
       </c>
       <c r="D2" t="n">
-        <v>10618</v>
+        <v>9791</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3362</v>
+        <v>3454</v>
       </c>
       <c r="C3" t="n">
-        <v>6025</v>
+        <v>4072</v>
       </c>
       <c r="D3" t="n">
-        <v>13627</v>
+        <v>14134</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3431</v>
+        <v>3627</v>
       </c>
       <c r="C4" t="n">
-        <v>5979</v>
+        <v>5678</v>
       </c>
       <c r="D4" t="n">
-        <v>12208</v>
+        <v>12888</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2646</v>
+        <v>2809</v>
       </c>
       <c r="C5" t="n">
-        <v>7931</v>
+        <v>7611</v>
       </c>
       <c r="D5" t="n">
-        <v>6064</v>
+        <v>6208</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1351</v>
+        <v>1517</v>
       </c>
       <c r="C6" t="n">
-        <v>7698</v>
+        <v>6797</v>
       </c>
       <c r="D6" t="n">
-        <v>2023</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>289</v>
+        <v>344</v>
       </c>
       <c r="C7" t="n">
-        <v>5304</v>
+        <v>4269</v>
       </c>
       <c r="D7" t="n">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>2590</v>
+        <v>2091</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>669</v>
+        <v>647</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4351</v>
+        <v>5781</v>
       </c>
       <c r="C2" t="n">
-        <v>18595</v>
+        <v>9189</v>
       </c>
       <c r="D2" t="n">
-        <v>13420</v>
+        <v>11432</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2707</v>
+        <v>2796</v>
       </c>
       <c r="C3" t="n">
-        <v>5323</v>
+        <v>3418</v>
       </c>
       <c r="D3" t="n">
-        <v>12439</v>
+        <v>12708</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2961</v>
+        <v>3129</v>
       </c>
       <c r="C4" t="n">
-        <v>5873</v>
+        <v>4881</v>
       </c>
       <c r="D4" t="n">
-        <v>12027</v>
+        <v>12675</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2671</v>
+        <v>2810</v>
       </c>
       <c r="C5" t="n">
-        <v>7016</v>
+        <v>6673</v>
       </c>
       <c r="D5" t="n">
-        <v>6588</v>
+        <v>6917</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1620</v>
+        <v>1813</v>
       </c>
       <c r="C6" t="n">
-        <v>7721</v>
+        <v>7052</v>
       </c>
       <c r="D6" t="n">
-        <v>2501</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>542</v>
+        <v>630</v>
       </c>
       <c r="C7" t="n">
-        <v>6146</v>
+        <v>5208</v>
       </c>
       <c r="D7" t="n">
-        <v>872</v>
+        <v>865</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="C8" t="n">
-        <v>3518</v>
+        <v>2879</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>1252</v>
+        <v>1120</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="D10" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>38</v>
+      </c>
+      <c r="D14" t="n">
         <v>37</v>
-      </c>
-      <c r="D14" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9797</v>
+        <v>8269</v>
       </c>
       <c r="C2" t="n">
-        <v>11470</v>
+        <v>7817</v>
       </c>
       <c r="D2" t="n">
-        <v>15739</v>
+        <v>7079</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3181</v>
+        <v>4134</v>
       </c>
       <c r="C2" t="n">
-        <v>11008</v>
+        <v>5293</v>
       </c>
       <c r="D2" t="n">
-        <v>9984</v>
+        <v>8414</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3628</v>
+        <v>3903</v>
       </c>
       <c r="C3" t="n">
-        <v>8625</v>
+        <v>5011</v>
       </c>
       <c r="D3" t="n">
-        <v>13616</v>
+        <v>13783</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3956</v>
+        <v>4171</v>
       </c>
       <c r="C4" t="n">
-        <v>8347</v>
+        <v>7127</v>
       </c>
       <c r="D4" t="n">
-        <v>12203</v>
+        <v>12976</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1521</v>
+        <v>1753</v>
       </c>
       <c r="C5" t="n">
-        <v>10582</v>
+        <v>9820</v>
       </c>
       <c r="D5" t="n">
-        <v>5993</v>
+        <v>6218</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>500</v>
+        <v>582</v>
       </c>
       <c r="C6" t="n">
-        <v>7385</v>
+        <v>6486</v>
       </c>
       <c r="D6" t="n">
-        <v>1952</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>3447</v>
+        <v>2821</v>
       </c>
       <c r="D7" t="n">
-        <v>526</v>
+        <v>547</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>1226</v>
+        <v>1097</v>
       </c>
       <c r="D8" t="n">
-        <v>284</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="D9" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>37</v>
+      </c>
+      <c r="D13" t="n">
         <v>36</v>
-      </c>
-      <c r="D13" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8318</v>
+        <v>7699</v>
       </c>
       <c r="C2" t="n">
-        <v>12095</v>
+        <v>3872</v>
       </c>
       <c r="D2" t="n">
-        <v>28725</v>
+        <v>12870</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4159</v>
+        <v>3511</v>
       </c>
       <c r="C3" t="n">
-        <v>5780</v>
+        <v>3939</v>
       </c>
       <c r="D3" t="n">
-        <v>3283</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="4">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4638,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
         <v>154</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5563</v>
+        <v>5728</v>
       </c>
       <c r="C2" t="n">
-        <v>6628</v>
+        <v>7905</v>
       </c>
       <c r="D2" t="n">
-        <v>26533</v>
+        <v>13851</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5098</v>
+        <v>4606</v>
       </c>
       <c r="C3" t="n">
-        <v>8025</v>
+        <v>3364</v>
       </c>
       <c r="D3" t="n">
-        <v>7117</v>
+        <v>3548</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1806</v>
+        <v>1559</v>
       </c>
       <c r="C4" t="n">
-        <v>3375</v>
+        <v>2351</v>
       </c>
       <c r="D4" t="n">
-        <v>1811</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4924,10 +4924,10 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4955,7 +4955,7 @@
         <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -4994,7 +4994,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>146</v>
@@ -5025,7 +5025,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6567</v>
+        <v>5882</v>
       </c>
       <c r="C2" t="n">
-        <v>9158</v>
+        <v>4644</v>
       </c>
       <c r="D2" t="n">
-        <v>25049</v>
+        <v>25007</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4394</v>
+        <v>4246</v>
       </c>
       <c r="C3" t="n">
-        <v>6335</v>
+        <v>5055</v>
       </c>
       <c r="D3" t="n">
-        <v>9567</v>
+        <v>4941</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2915</v>
+        <v>2613</v>
       </c>
       <c r="C4" t="n">
-        <v>5816</v>
+        <v>2875</v>
       </c>
       <c r="D4" t="n">
-        <v>2706</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>772</v>
+        <v>699</v>
       </c>
       <c r="C5" t="n">
-        <v>1913</v>
+        <v>1381</v>
       </c>
       <c r="D5" t="n">
-        <v>1273</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5364,7 +5364,7 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5403,10 +5403,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5902</v>
+        <v>5820</v>
       </c>
       <c r="C2" t="n">
-        <v>6599</v>
+        <v>5128</v>
       </c>
       <c r="D2" t="n">
-        <v>23387</v>
+        <v>31906</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4423</v>
+        <v>4128</v>
       </c>
       <c r="C3" t="n">
-        <v>6753</v>
+        <v>4215</v>
       </c>
       <c r="D3" t="n">
-        <v>11138</v>
+        <v>7643</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3075</v>
+        <v>2924</v>
       </c>
       <c r="C4" t="n">
-        <v>5964</v>
+        <v>3987</v>
       </c>
       <c r="D4" t="n">
-        <v>3783</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1506</v>
+        <v>1363</v>
       </c>
       <c r="C5" t="n">
-        <v>3803</v>
+        <v>2113</v>
       </c>
       <c r="D5" t="n">
-        <v>1481</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="C6" t="n">
-        <v>1091</v>
+        <v>847</v>
       </c>
       <c r="D6" t="n">
-        <v>937</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>477</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5714,10 +5714,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6845</v>
+        <v>6159</v>
       </c>
       <c r="C2" t="n">
-        <v>10565</v>
+        <v>8784</v>
       </c>
       <c r="D2" t="n">
-        <v>30484</v>
+        <v>31637</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3713</v>
+        <v>3602</v>
       </c>
       <c r="C3" t="n">
-        <v>5536</v>
+        <v>3835</v>
       </c>
       <c r="D3" t="n">
-        <v>11407</v>
+        <v>10152</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2285</v>
+        <v>2175</v>
       </c>
       <c r="C4" t="n">
-        <v>5158</v>
+        <v>3368</v>
       </c>
       <c r="D4" t="n">
-        <v>4271</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1190</v>
+        <v>1127</v>
       </c>
       <c r="C5" t="n">
-        <v>3555</v>
+        <v>2239</v>
       </c>
       <c r="D5" t="n">
-        <v>1485</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="C6" t="n">
-        <v>1592</v>
+        <v>1000</v>
       </c>
       <c r="D6" t="n">
-        <v>772</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>446</v>
+        <v>378</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6853</v>
+        <v>6934</v>
       </c>
       <c r="C2" t="n">
-        <v>9068</v>
+        <v>3926</v>
       </c>
       <c r="D2" t="n">
-        <v>29980</v>
+        <v>39515</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4374</v>
+        <v>4053</v>
       </c>
       <c r="C3" t="n">
-        <v>7228</v>
+        <v>5789</v>
       </c>
       <c r="D3" t="n">
-        <v>13772</v>
+        <v>13014</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2574</v>
+        <v>2534</v>
       </c>
       <c r="C4" t="n">
-        <v>5272</v>
+        <v>3548</v>
       </c>
       <c r="D4" t="n">
-        <v>5579</v>
+        <v>4211</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1536</v>
+        <v>1465</v>
       </c>
       <c r="C5" t="n">
-        <v>4388</v>
+        <v>2864</v>
       </c>
       <c r="D5" t="n">
-        <v>1974</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>730</v>
+        <v>714</v>
       </c>
       <c r="C6" t="n">
-        <v>2647</v>
+        <v>1701</v>
       </c>
       <c r="D6" t="n">
-        <v>883</v>
+        <v>818</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C7" t="n">
-        <v>1063</v>
+        <v>731</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>335</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
         <v>240</v>
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6322,10 +6322,10 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6475</v>
+        <v>5494</v>
       </c>
       <c r="C2" t="n">
-        <v>5853</v>
+        <v>7025</v>
       </c>
       <c r="D2" t="n">
-        <v>28289</v>
+        <v>34147</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4534</v>
+        <v>4479</v>
       </c>
       <c r="C3" t="n">
-        <v>7115</v>
+        <v>4131</v>
       </c>
       <c r="D3" t="n">
-        <v>15266</v>
+        <v>16317</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2920</v>
+        <v>2836</v>
       </c>
       <c r="C4" t="n">
-        <v>6213</v>
+        <v>4743</v>
       </c>
       <c r="D4" t="n">
-        <v>6903</v>
+        <v>5773</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1795</v>
+        <v>1745</v>
       </c>
       <c r="C5" t="n">
-        <v>4754</v>
+        <v>3178</v>
       </c>
       <c r="D5" t="n">
-        <v>2517</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1001</v>
+        <v>992</v>
       </c>
       <c r="C6" t="n">
-        <v>3461</v>
+        <v>2279</v>
       </c>
       <c r="D6" t="n">
-        <v>1059</v>
+        <v>922</v>
       </c>
     </row>
     <row r="7">
@@ -6451,10 +6451,10 @@
         <v>413</v>
       </c>
       <c r="C7" t="n">
-        <v>1854</v>
+        <v>1244</v>
       </c>
       <c r="D7" t="n">
-        <v>602</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>684</v>
+        <v>522</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_81_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_81_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6230</v>
+        <v>4586</v>
       </c>
       <c r="C2" t="n">
-        <v>7325</v>
+        <v>6599</v>
       </c>
       <c r="D2" t="n">
-        <v>26899</v>
+        <v>14121</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4076</v>
+        <v>3157</v>
       </c>
       <c r="C3" t="n">
-        <v>4859</v>
+        <v>5755</v>
       </c>
       <c r="D3" t="n">
-        <v>17761</v>
+        <v>9421</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3070</v>
+        <v>2490</v>
       </c>
       <c r="C4" t="n">
-        <v>4281</v>
+        <v>5443</v>
       </c>
       <c r="D4" t="n">
-        <v>7364</v>
+        <v>4951</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1998</v>
+        <v>1672</v>
       </c>
       <c r="C5" t="n">
-        <v>3908</v>
+        <v>4511</v>
       </c>
       <c r="D5" t="n">
-        <v>2509</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1217</v>
+        <v>991</v>
       </c>
       <c r="C6" t="n">
-        <v>2672</v>
+        <v>3363</v>
       </c>
       <c r="D6" t="n">
-        <v>1059</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>604</v>
+        <v>477</v>
       </c>
       <c r="C7" t="n">
-        <v>1750</v>
+        <v>2110</v>
       </c>
       <c r="D7" t="n">
-        <v>640</v>
+        <v>634</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>228</v>
+        <v>177</v>
       </c>
       <c r="C8" t="n">
-        <v>861</v>
+        <v>1040</v>
       </c>
       <c r="D8" t="n">
         <v>432</v>
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>373</v>
+        <v>417</v>
       </c>
       <c r="D9" t="n">
         <v>310</v>
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
         <v>244</v>
@@ -909,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10142</v>
+        <v>7162</v>
       </c>
       <c r="C2" t="n">
-        <v>12204</v>
+        <v>6861</v>
       </c>
       <c r="D2" t="n">
-        <v>25182</v>
+        <v>14921</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4107</v>
+        <v>3100</v>
       </c>
       <c r="C3" t="n">
-        <v>5262</v>
+        <v>5399</v>
       </c>
       <c r="D3" t="n">
-        <v>17810</v>
+        <v>9427</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3027</v>
+        <v>2381</v>
       </c>
       <c r="C4" t="n">
-        <v>4428</v>
+        <v>5482</v>
       </c>
       <c r="D4" t="n">
-        <v>8836</v>
+        <v>5482</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2172</v>
+        <v>1796</v>
       </c>
       <c r="C5" t="n">
-        <v>4002</v>
+        <v>4812</v>
       </c>
       <c r="D5" t="n">
-        <v>3154</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1417</v>
+        <v>1185</v>
       </c>
       <c r="C6" t="n">
-        <v>3177</v>
+        <v>3858</v>
       </c>
       <c r="D6" t="n">
-        <v>1267</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="7">
@@ -1161,10 +1161,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>784</v>
+        <v>625</v>
       </c>
       <c r="C7" t="n">
-        <v>2164</v>
+        <v>2653</v>
       </c>
       <c r="D7" t="n">
         <v>688</v>
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>337</v>
+        <v>267</v>
       </c>
       <c r="C8" t="n">
-        <v>1235</v>
+        <v>1511</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>578</v>
+        <v>675</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10297</v>
+        <v>9238</v>
       </c>
       <c r="C2" t="n">
-        <v>13466</v>
+        <v>8997</v>
       </c>
       <c r="D2" t="n">
-        <v>29533</v>
+        <v>16561</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5252</v>
+        <v>3845</v>
       </c>
       <c r="C3" t="n">
-        <v>7218</v>
+        <v>5326</v>
       </c>
       <c r="D3" t="n">
-        <v>17585</v>
+        <v>9511</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2954</v>
+        <v>2287</v>
       </c>
       <c r="C4" t="n">
-        <v>4704</v>
+        <v>5330</v>
       </c>
       <c r="D4" t="n">
-        <v>9945</v>
+        <v>5921</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2238</v>
+        <v>1832</v>
       </c>
       <c r="C5" t="n">
-        <v>4060</v>
+        <v>4955</v>
       </c>
       <c r="D5" t="n">
-        <v>3846</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1573</v>
+        <v>1309</v>
       </c>
       <c r="C6" t="n">
-        <v>3457</v>
+        <v>4225</v>
       </c>
       <c r="D6" t="n">
-        <v>1522</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>943</v>
+        <v>764</v>
       </c>
       <c r="C7" t="n">
-        <v>2580</v>
+        <v>3121</v>
       </c>
       <c r="D7" t="n">
-        <v>753</v>
+        <v>738</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>450</v>
+        <v>361</v>
       </c>
       <c r="C8" t="n">
-        <v>1586</v>
+        <v>1954</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="C9" t="n">
-        <v>823</v>
+        <v>1002</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>389</v>
+        <v>436</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>103</v>
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9367</v>
+        <v>8218</v>
       </c>
       <c r="C2" t="n">
-        <v>9156</v>
+        <v>6045</v>
       </c>
       <c r="D2" t="n">
-        <v>24301</v>
+        <v>13614</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5872</v>
+        <v>4405</v>
       </c>
       <c r="C3" t="n">
-        <v>10441</v>
+        <v>8362</v>
       </c>
       <c r="D3" t="n">
-        <v>19261</v>
+        <v>10527</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2067</v>
+        <v>1692</v>
       </c>
       <c r="C4" t="n">
-        <v>6516</v>
+        <v>7775</v>
       </c>
       <c r="D4" t="n">
-        <v>9150</v>
+        <v>5831</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1453</v>
+        <v>1209</v>
       </c>
       <c r="C5" t="n">
-        <v>3387</v>
+        <v>4140</v>
       </c>
       <c r="D5" t="n">
-        <v>2525</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>871</v>
+        <v>705</v>
       </c>
       <c r="C6" t="n">
-        <v>2528</v>
+        <v>3058</v>
       </c>
       <c r="D6" t="n">
-        <v>737</v>
+        <v>723</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>415</v>
+        <v>333</v>
       </c>
       <c r="C7" t="n">
-        <v>1554</v>
+        <v>1914</v>
       </c>
       <c r="D7" t="n">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>806</v>
+        <v>981</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>381</v>
+        <v>427</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
         <v>77</v>
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5529</v>
+        <v>4874</v>
       </c>
       <c r="C2" t="n">
-        <v>3907</v>
+        <v>3200</v>
       </c>
       <c r="D2" t="n">
-        <v>16767</v>
+        <v>9958</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6299</v>
+        <v>5134</v>
       </c>
       <c r="C3" t="n">
-        <v>9021</v>
+        <v>6657</v>
       </c>
       <c r="D3" t="n">
-        <v>18837</v>
+        <v>10340</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3021</v>
+        <v>2380</v>
       </c>
       <c r="C4" t="n">
-        <v>8376</v>
+        <v>8113</v>
       </c>
       <c r="D4" t="n">
-        <v>10600</v>
+        <v>6486</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1608</v>
+        <v>1335</v>
       </c>
       <c r="C5" t="n">
-        <v>4770</v>
+        <v>5788</v>
       </c>
       <c r="D5" t="n">
-        <v>3323</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1021</v>
+        <v>838</v>
       </c>
       <c r="C6" t="n">
-        <v>2954</v>
+        <v>3598</v>
       </c>
       <c r="D6" t="n">
-        <v>921</v>
+        <v>866</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>392</v>
+        <v>317</v>
       </c>
       <c r="C7" t="n">
-        <v>1957</v>
+        <v>2407</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>1051</v>
+        <v>1289</v>
       </c>
       <c r="D8" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>428</v>
+        <v>486</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="D10" t="n">
         <v>212</v>
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
         <v>97</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6077</v>
+        <v>5526</v>
       </c>
       <c r="C2" t="n">
-        <v>5630</v>
+        <v>7921</v>
       </c>
       <c r="D2" t="n">
-        <v>16395</v>
+        <v>13866</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5068</v>
+        <v>4208</v>
       </c>
       <c r="C3" t="n">
-        <v>5868</v>
+        <v>4424</v>
       </c>
       <c r="D3" t="n">
-        <v>17423</v>
+        <v>9573</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3770</v>
+        <v>3097</v>
       </c>
       <c r="C4" t="n">
-        <v>8517</v>
+        <v>7217</v>
       </c>
       <c r="D4" t="n">
-        <v>11622</v>
+        <v>6954</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1954</v>
+        <v>1588</v>
       </c>
       <c r="C5" t="n">
-        <v>6367</v>
+        <v>6783</v>
       </c>
       <c r="D5" t="n">
-        <v>4339</v>
+        <v>3097</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1166</v>
+        <v>975</v>
       </c>
       <c r="C6" t="n">
-        <v>3773</v>
+        <v>4606</v>
       </c>
       <c r="D6" t="n">
-        <v>1254</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>568</v>
+        <v>460</v>
       </c>
       <c r="C7" t="n">
-        <v>2405</v>
+        <v>2954</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="C8" t="n">
-        <v>1424</v>
+        <v>1761</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>664</v>
+        <v>797</v>
       </c>
       <c r="D9" t="n">
         <v>265</v>
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="D10" t="n">
         <v>216</v>
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
         <v>170</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3614</v>
+        <v>3209</v>
       </c>
       <c r="C2" t="n">
-        <v>2628</v>
+        <v>3650</v>
       </c>
       <c r="D2" t="n">
-        <v>11488</v>
+        <v>9558</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5123</v>
+        <v>4373</v>
       </c>
       <c r="C3" t="n">
-        <v>5609</v>
+        <v>5485</v>
       </c>
       <c r="D3" t="n">
-        <v>16925</v>
+        <v>9824</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4177</v>
+        <v>3455</v>
       </c>
       <c r="C4" t="n">
-        <v>8292</v>
+        <v>6821</v>
       </c>
       <c r="D4" t="n">
-        <v>12369</v>
+        <v>7327</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2047</v>
+        <v>1684</v>
       </c>
       <c r="C5" t="n">
-        <v>7790</v>
+        <v>7829</v>
       </c>
       <c r="D5" t="n">
-        <v>4593</v>
+        <v>3348</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>998</v>
+        <v>830</v>
       </c>
       <c r="C6" t="n">
-        <v>4572</v>
+        <v>5686</v>
       </c>
       <c r="D6" t="n">
-        <v>1232</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="C7" t="n">
-        <v>2565</v>
+        <v>3171</v>
       </c>
       <c r="D7" t="n">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1083</v>
+        <v>1333</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>295</v>
+        <v>323</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
         <v>166</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4143</v>
+        <v>3949</v>
       </c>
       <c r="C2" t="n">
-        <v>5441</v>
+        <v>12537</v>
       </c>
       <c r="D2" t="n">
-        <v>13139</v>
+        <v>11575</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3847</v>
+        <v>3313</v>
       </c>
       <c r="C3" t="n">
-        <v>3797</v>
+        <v>4098</v>
       </c>
       <c r="D3" t="n">
-        <v>15210</v>
+        <v>9127</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3979</v>
+        <v>3344</v>
       </c>
       <c r="C4" t="n">
-        <v>6857</v>
+        <v>6090</v>
       </c>
       <c r="D4" t="n">
-        <v>12692</v>
+        <v>7511</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2567</v>
+        <v>2131</v>
       </c>
       <c r="C5" t="n">
-        <v>7929</v>
+        <v>7276</v>
       </c>
       <c r="D5" t="n">
-        <v>5573</v>
+        <v>3857</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1278</v>
+        <v>1065</v>
       </c>
       <c r="C6" t="n">
-        <v>5934</v>
+        <v>6614</v>
       </c>
       <c r="D6" t="n">
-        <v>1667</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>381</v>
+        <v>324</v>
       </c>
       <c r="C7" t="n">
-        <v>3420</v>
+        <v>4267</v>
       </c>
       <c r="D7" t="n">
-        <v>653</v>
+        <v>630</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>1641</v>
+        <v>2043</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>558</v>
+        <v>668</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3084</v>
+        <v>2691</v>
       </c>
       <c r="C2" t="n">
-        <v>3414</v>
+        <v>5875</v>
       </c>
       <c r="D2" t="n">
-        <v>9791</v>
+        <v>8643</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3454</v>
+        <v>3084</v>
       </c>
       <c r="C3" t="n">
-        <v>4072</v>
+        <v>6856</v>
       </c>
       <c r="D3" t="n">
-        <v>14134</v>
+        <v>8924</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3627</v>
+        <v>3068</v>
       </c>
       <c r="C4" t="n">
-        <v>5678</v>
+        <v>5257</v>
       </c>
       <c r="D4" t="n">
-        <v>12888</v>
+        <v>7571</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2809</v>
+        <v>2348</v>
       </c>
       <c r="C5" t="n">
-        <v>7611</v>
+        <v>6960</v>
       </c>
       <c r="D5" t="n">
-        <v>6208</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1517</v>
+        <v>1270</v>
       </c>
       <c r="C6" t="n">
-        <v>6797</v>
+        <v>7101</v>
       </c>
       <c r="D6" t="n">
-        <v>2033</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>344</v>
+        <v>305</v>
       </c>
       <c r="C7" t="n">
-        <v>4269</v>
+        <v>5156</v>
       </c>
       <c r="D7" t="n">
-        <v>726</v>
+        <v>696</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>2091</v>
+        <v>2619</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>647</v>
+        <v>796</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5781</v>
+        <v>3677</v>
       </c>
       <c r="C2" t="n">
-        <v>9189</v>
+        <v>6025</v>
       </c>
       <c r="D2" t="n">
-        <v>11432</v>
+        <v>9251</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2796</v>
+        <v>2473</v>
       </c>
       <c r="C3" t="n">
-        <v>3418</v>
+        <v>5781</v>
       </c>
       <c r="D3" t="n">
-        <v>12708</v>
+        <v>8319</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3129</v>
+        <v>2697</v>
       </c>
       <c r="C4" t="n">
-        <v>4881</v>
+        <v>5838</v>
       </c>
       <c r="D4" t="n">
-        <v>12675</v>
+        <v>7535</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2810</v>
+        <v>2364</v>
       </c>
       <c r="C5" t="n">
-        <v>6673</v>
+        <v>6112</v>
       </c>
       <c r="D5" t="n">
-        <v>6917</v>
+        <v>4513</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1813</v>
+        <v>1527</v>
       </c>
       <c r="C6" t="n">
-        <v>7052</v>
+        <v>6984</v>
       </c>
       <c r="D6" t="n">
-        <v>2528</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>630</v>
+        <v>548</v>
       </c>
       <c r="C7" t="n">
-        <v>5208</v>
+        <v>5897</v>
       </c>
       <c r="D7" t="n">
-        <v>865</v>
+        <v>810</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>2879</v>
+        <v>3563</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1120</v>
+        <v>1410</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>352</v>
+        <v>409</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>39</v>
+      </c>
+      <c r="D14" t="n">
         <v>38</v>
-      </c>
-      <c r="D14" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8269</v>
+        <v>5326</v>
       </c>
       <c r="C2" t="n">
-        <v>7817</v>
+        <v>8027</v>
       </c>
       <c r="D2" t="n">
-        <v>7079</v>
+        <v>6406</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4134</v>
+        <v>2602</v>
       </c>
       <c r="C2" t="n">
-        <v>5293</v>
+        <v>3423</v>
       </c>
       <c r="D2" t="n">
-        <v>8414</v>
+        <v>6808</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3903</v>
+        <v>3310</v>
       </c>
       <c r="C3" t="n">
-        <v>5011</v>
+        <v>6337</v>
       </c>
       <c r="D3" t="n">
-        <v>13783</v>
+        <v>9084</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4171</v>
+        <v>3566</v>
       </c>
       <c r="C4" t="n">
-        <v>7127</v>
+        <v>8092</v>
       </c>
       <c r="D4" t="n">
-        <v>12976</v>
+        <v>7767</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1753</v>
+        <v>1476</v>
       </c>
       <c r="C5" t="n">
-        <v>9820</v>
+        <v>9396</v>
       </c>
       <c r="D5" t="n">
-        <v>6218</v>
+        <v>4259</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>582</v>
+        <v>506</v>
       </c>
       <c r="C6" t="n">
-        <v>6486</v>
+        <v>7216</v>
       </c>
       <c r="D6" t="n">
-        <v>1976</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C7" t="n">
-        <v>2821</v>
+        <v>3491</v>
       </c>
       <c r="D7" t="n">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1097</v>
+        <v>1381</v>
       </c>
       <c r="D8" t="n">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>344</v>
+        <v>400</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>38</v>
+      </c>
+      <c r="D13" t="n">
         <v>37</v>
-      </c>
-      <c r="D13" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7699</v>
+        <v>6788</v>
       </c>
       <c r="C2" t="n">
-        <v>3872</v>
+        <v>8893</v>
       </c>
       <c r="D2" t="n">
-        <v>12870</v>
+        <v>12436</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3511</v>
+        <v>2263</v>
       </c>
       <c r="C3" t="n">
-        <v>3939</v>
+        <v>4045</v>
       </c>
       <c r="D3" t="n">
-        <v>1828</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4557,7 +4557,7 @@
         <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5728</v>
+        <v>4225</v>
       </c>
       <c r="C2" t="n">
-        <v>7905</v>
+        <v>4971</v>
       </c>
       <c r="D2" t="n">
-        <v>13851</v>
+        <v>11448</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4606</v>
+        <v>3714</v>
       </c>
       <c r="C3" t="n">
-        <v>3364</v>
+        <v>5854</v>
       </c>
       <c r="D3" t="n">
-        <v>3548</v>
+        <v>3389</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1559</v>
+        <v>1016</v>
       </c>
       <c r="C4" t="n">
-        <v>2351</v>
+        <v>2412</v>
       </c>
       <c r="D4" t="n">
-        <v>1549</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
         <v>864</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5882</v>
+        <v>5557</v>
       </c>
       <c r="C2" t="n">
-        <v>4644</v>
+        <v>7533</v>
       </c>
       <c r="D2" t="n">
-        <v>25007</v>
+        <v>16420</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4246</v>
+        <v>3270</v>
       </c>
       <c r="C3" t="n">
-        <v>5055</v>
+        <v>4650</v>
       </c>
       <c r="D3" t="n">
-        <v>4941</v>
+        <v>4434</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2613</v>
+        <v>2000</v>
       </c>
       <c r="C4" t="n">
-        <v>2875</v>
+        <v>4311</v>
       </c>
       <c r="D4" t="n">
-        <v>1885</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>699</v>
+        <v>477</v>
       </c>
       <c r="C5" t="n">
-        <v>1381</v>
+        <v>1414</v>
       </c>
       <c r="D5" t="n">
-        <v>1204</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="6">
@@ -5190,7 +5190,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
         <v>301</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -5218,7 +5218,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
         <v>358</v>
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
@@ -5280,7 +5280,7 @@
         <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5820</v>
+        <v>4760</v>
       </c>
       <c r="C2" t="n">
-        <v>5128</v>
+        <v>7333</v>
       </c>
       <c r="D2" t="n">
-        <v>31906</v>
+        <v>17244</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4128</v>
+        <v>3566</v>
       </c>
       <c r="C3" t="n">
-        <v>4215</v>
+        <v>5338</v>
       </c>
       <c r="D3" t="n">
-        <v>7643</v>
+        <v>5943</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2924</v>
+        <v>2246</v>
       </c>
       <c r="C4" t="n">
-        <v>3987</v>
+        <v>4362</v>
       </c>
       <c r="D4" t="n">
-        <v>2385</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1363</v>
+        <v>1013</v>
       </c>
       <c r="C5" t="n">
-        <v>2113</v>
+        <v>2914</v>
       </c>
       <c r="D5" t="n">
-        <v>1273</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>363</v>
+        <v>272</v>
       </c>
       <c r="C6" t="n">
-        <v>847</v>
+        <v>863</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -5515,7 +5515,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
@@ -5557,7 +5557,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
         <v>234</v>
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
         <v>187</v>
@@ -5591,7 +5591,7 @@
         <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6159</v>
+        <v>5454</v>
       </c>
       <c r="C2" t="n">
-        <v>8784</v>
+        <v>8024</v>
       </c>
       <c r="D2" t="n">
-        <v>31637</v>
+        <v>19070</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3602</v>
+        <v>3020</v>
       </c>
       <c r="C3" t="n">
-        <v>3835</v>
+        <v>5208</v>
       </c>
       <c r="D3" t="n">
-        <v>10152</v>
+        <v>6813</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2175</v>
+        <v>1791</v>
       </c>
       <c r="C4" t="n">
-        <v>3368</v>
+        <v>3981</v>
       </c>
       <c r="D4" t="n">
-        <v>2855</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1127</v>
+        <v>849</v>
       </c>
       <c r="C5" t="n">
-        <v>2239</v>
+        <v>2687</v>
       </c>
       <c r="D5" t="n">
-        <v>1145</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>404</v>
+        <v>307</v>
       </c>
       <c r="C6" t="n">
-        <v>1000</v>
+        <v>1277</v>
       </c>
       <c r="D6" t="n">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="D7" t="n">
         <v>513</v>
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
         <v>270</v>
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6934</v>
+        <v>4752</v>
       </c>
       <c r="C2" t="n">
-        <v>3926</v>
+        <v>7342</v>
       </c>
       <c r="D2" t="n">
-        <v>39515</v>
+        <v>16362</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4053</v>
+        <v>3521</v>
       </c>
       <c r="C3" t="n">
-        <v>5789</v>
+        <v>5908</v>
       </c>
       <c r="D3" t="n">
-        <v>13014</v>
+        <v>8457</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2534</v>
+        <v>2096</v>
       </c>
       <c r="C4" t="n">
-        <v>3548</v>
+        <v>4652</v>
       </c>
       <c r="D4" t="n">
-        <v>4211</v>
+        <v>3328</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1465</v>
+        <v>1185</v>
       </c>
       <c r="C5" t="n">
-        <v>2864</v>
+        <v>3401</v>
       </c>
       <c r="D5" t="n">
-        <v>1454</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>714</v>
+        <v>539</v>
       </c>
       <c r="C6" t="n">
-        <v>1701</v>
+        <v>2073</v>
       </c>
       <c r="D6" t="n">
-        <v>818</v>
+        <v>811</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>233</v>
+        <v>180</v>
       </c>
       <c r="C7" t="n">
-        <v>731</v>
+        <v>890</v>
       </c>
       <c r="D7" t="n">
         <v>556</v>
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
         <v>388</v>
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
         <v>240</v>
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>120</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>64</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5494</v>
+        <v>4329</v>
       </c>
       <c r="C2" t="n">
-        <v>7025</v>
+        <v>7338</v>
       </c>
       <c r="D2" t="n">
-        <v>34147</v>
+        <v>15369</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4479</v>
+        <v>3400</v>
       </c>
       <c r="C3" t="n">
-        <v>4131</v>
+        <v>5849</v>
       </c>
       <c r="D3" t="n">
-        <v>16317</v>
+        <v>9112</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2836</v>
+        <v>2428</v>
       </c>
       <c r="C4" t="n">
-        <v>4743</v>
+        <v>5221</v>
       </c>
       <c r="D4" t="n">
-        <v>5773</v>
+        <v>4179</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1745</v>
+        <v>1448</v>
       </c>
       <c r="C5" t="n">
-        <v>3178</v>
+        <v>4026</v>
       </c>
       <c r="D5" t="n">
-        <v>1898</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>992</v>
+        <v>777</v>
       </c>
       <c r="C6" t="n">
-        <v>2279</v>
+        <v>2762</v>
       </c>
       <c r="D6" t="n">
-        <v>922</v>
+        <v>900</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>413</v>
+        <v>318</v>
       </c>
       <c r="C7" t="n">
-        <v>1244</v>
+        <v>1515</v>
       </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>522</v>
+        <v>602</v>
       </c>
       <c r="D8" t="n">
         <v>413</v>
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D9" t="n">
         <v>295</v>
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
         <v>241</v>
@@ -6524,7 +6524,7 @@
         <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6594,7 +6594,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6633,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_81_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_81_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4586</v>
+        <v>788</v>
       </c>
       <c r="C2" t="n">
-        <v>6599</v>
+        <v>4967</v>
       </c>
       <c r="D2" t="n">
-        <v>14121</v>
+        <v>11018</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3157</v>
+        <v>1873</v>
       </c>
       <c r="C3" t="n">
-        <v>5755</v>
+        <v>9883</v>
       </c>
       <c r="D3" t="n">
-        <v>9421</v>
+        <v>11392</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2490</v>
+        <v>1596</v>
       </c>
       <c r="C4" t="n">
-        <v>5443</v>
+        <v>11112</v>
       </c>
       <c r="D4" t="n">
-        <v>4951</v>
+        <v>5179</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1672</v>
+        <v>819</v>
       </c>
       <c r="C5" t="n">
-        <v>4511</v>
+        <v>7986</v>
       </c>
       <c r="D5" t="n">
-        <v>2058</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>991</v>
+        <v>319</v>
       </c>
       <c r="C6" t="n">
-        <v>3363</v>
+        <v>3598</v>
       </c>
       <c r="D6" t="n">
-        <v>1025</v>
+        <v>709</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>477</v>
+        <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>2110</v>
+        <v>1169</v>
       </c>
       <c r="D7" t="n">
-        <v>634</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>177</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>1040</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>417</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>139</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7162</v>
+        <v>1233</v>
       </c>
       <c r="C2" t="n">
-        <v>6861</v>
+        <v>11378</v>
       </c>
       <c r="D2" t="n">
-        <v>14921</v>
+        <v>11828</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3100</v>
+        <v>1186</v>
       </c>
       <c r="C3" t="n">
-        <v>5399</v>
+        <v>6604</v>
       </c>
       <c r="D3" t="n">
-        <v>9427</v>
+        <v>10554</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2381</v>
+        <v>1502</v>
       </c>
       <c r="C4" t="n">
-        <v>5482</v>
+        <v>10255</v>
       </c>
       <c r="D4" t="n">
-        <v>5482</v>
+        <v>6095</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1796</v>
+        <v>1020</v>
       </c>
       <c r="C5" t="n">
-        <v>4812</v>
+        <v>9427</v>
       </c>
       <c r="D5" t="n">
-        <v>2467</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1185</v>
+        <v>474</v>
       </c>
       <c r="C6" t="n">
-        <v>3858</v>
+        <v>5619</v>
       </c>
       <c r="D6" t="n">
-        <v>1159</v>
+        <v>854</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>625</v>
+        <v>164</v>
       </c>
       <c r="C7" t="n">
-        <v>2653</v>
+        <v>2251</v>
       </c>
       <c r="D7" t="n">
-        <v>688</v>
+        <v>507</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>267</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>1511</v>
+        <v>708</v>
       </c>
       <c r="D8" t="n">
-        <v>453</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>675</v>
+        <v>313</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>300</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9238</v>
+        <v>694</v>
       </c>
       <c r="C2" t="n">
-        <v>8997</v>
+        <v>5154</v>
       </c>
       <c r="D2" t="n">
-        <v>16561</v>
+        <v>8176</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3845</v>
+        <v>1154</v>
       </c>
       <c r="C3" t="n">
-        <v>5326</v>
+        <v>8062</v>
       </c>
       <c r="D3" t="n">
-        <v>9511</v>
+        <v>10443</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2287</v>
+        <v>1610</v>
       </c>
       <c r="C4" t="n">
-        <v>5330</v>
+        <v>9764</v>
       </c>
       <c r="D4" t="n">
-        <v>5921</v>
+        <v>6630</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1832</v>
+        <v>1004</v>
       </c>
       <c r="C5" t="n">
-        <v>4955</v>
+        <v>10999</v>
       </c>
       <c r="D5" t="n">
-        <v>2802</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1309</v>
+        <v>348</v>
       </c>
       <c r="C6" t="n">
-        <v>4225</v>
+        <v>6603</v>
       </c>
       <c r="D6" t="n">
-        <v>1332</v>
+        <v>872</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>764</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>3121</v>
+        <v>1993</v>
       </c>
       <c r="D7" t="n">
-        <v>738</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>361</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1954</v>
+        <v>528</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>145</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>1002</v>
+        <v>225</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>436</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>226</v>
+        <v>121</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8218</v>
+        <v>1298</v>
       </c>
       <c r="C2" t="n">
-        <v>6045</v>
+        <v>5718</v>
       </c>
       <c r="D2" t="n">
-        <v>13614</v>
+        <v>10460</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4405</v>
+        <v>823</v>
       </c>
       <c r="C3" t="n">
-        <v>8362</v>
+        <v>5972</v>
       </c>
       <c r="D3" t="n">
-        <v>10527</v>
+        <v>9432</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1692</v>
+        <v>1257</v>
       </c>
       <c r="C4" t="n">
-        <v>7775</v>
+        <v>8743</v>
       </c>
       <c r="D4" t="n">
-        <v>5831</v>
+        <v>7050</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1209</v>
+        <v>1138</v>
       </c>
       <c r="C5" t="n">
-        <v>4140</v>
+        <v>10306</v>
       </c>
       <c r="D5" t="n">
-        <v>2085</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>705</v>
+        <v>528</v>
       </c>
       <c r="C6" t="n">
-        <v>3058</v>
+        <v>8569</v>
       </c>
       <c r="D6" t="n">
-        <v>723</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>333</v>
+        <v>140</v>
       </c>
       <c r="C7" t="n">
-        <v>1914</v>
+        <v>3883</v>
       </c>
       <c r="D7" t="n">
-        <v>470</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>981</v>
+        <v>1069</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>427</v>
+        <v>329</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
+        <v>77</v>
+      </c>
+      <c r="D13" t="n">
         <v>89</v>
-      </c>
-      <c r="D13" t="n">
-        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4874</v>
+        <v>715</v>
       </c>
       <c r="C2" t="n">
-        <v>3200</v>
+        <v>3306</v>
       </c>
       <c r="D2" t="n">
-        <v>9958</v>
+        <v>7637</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5134</v>
+        <v>857</v>
       </c>
       <c r="C3" t="n">
-        <v>6657</v>
+        <v>5372</v>
       </c>
       <c r="D3" t="n">
-        <v>10340</v>
+        <v>9042</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2380</v>
+        <v>1042</v>
       </c>
       <c r="C4" t="n">
-        <v>8113</v>
+        <v>7669</v>
       </c>
       <c r="D4" t="n">
-        <v>6486</v>
+        <v>7223</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1335</v>
+        <v>1161</v>
       </c>
       <c r="C5" t="n">
-        <v>5788</v>
+        <v>9818</v>
       </c>
       <c r="D5" t="n">
-        <v>2529</v>
+        <v>3473</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>838</v>
+        <v>630</v>
       </c>
       <c r="C6" t="n">
-        <v>3598</v>
+        <v>9563</v>
       </c>
       <c r="D6" t="n">
-        <v>866</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>317</v>
+        <v>136</v>
       </c>
       <c r="C7" t="n">
-        <v>2407</v>
+        <v>5295</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>638</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1289</v>
+        <v>1616</v>
       </c>
       <c r="D8" t="n">
-        <v>340</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>486</v>
+        <v>405</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5526</v>
+        <v>735</v>
       </c>
       <c r="C2" t="n">
-        <v>7921</v>
+        <v>7163</v>
       </c>
       <c r="D2" t="n">
-        <v>13866</v>
+        <v>14029</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4208</v>
+        <v>678</v>
       </c>
       <c r="C3" t="n">
-        <v>4424</v>
+        <v>4026</v>
       </c>
       <c r="D3" t="n">
-        <v>9573</v>
+        <v>8294</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3097</v>
+        <v>848</v>
       </c>
       <c r="C4" t="n">
-        <v>7217</v>
+        <v>6517</v>
       </c>
       <c r="D4" t="n">
-        <v>6954</v>
+        <v>7265</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1588</v>
+        <v>1031</v>
       </c>
       <c r="C5" t="n">
-        <v>6783</v>
+        <v>8726</v>
       </c>
       <c r="D5" t="n">
-        <v>3097</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>975</v>
+        <v>756</v>
       </c>
       <c r="C6" t="n">
-        <v>4606</v>
+        <v>9581</v>
       </c>
       <c r="D6" t="n">
-        <v>1109</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>460</v>
+        <v>263</v>
       </c>
       <c r="C7" t="n">
-        <v>2954</v>
+        <v>6976</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>709</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>165</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>1761</v>
+        <v>2929</v>
       </c>
       <c r="D8" t="n">
-        <v>363</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>330</v>
+        <v>271</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
+        <v>65</v>
+      </c>
+      <c r="D14" t="n">
         <v>54</v>
-      </c>
-      <c r="D14" t="n">
-        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3209</v>
+        <v>523</v>
       </c>
       <c r="C2" t="n">
-        <v>3650</v>
+        <v>4068</v>
       </c>
       <c r="D2" t="n">
-        <v>9558</v>
+        <v>10325</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4373</v>
+        <v>909</v>
       </c>
       <c r="C3" t="n">
-        <v>5485</v>
+        <v>5101</v>
       </c>
       <c r="D3" t="n">
-        <v>9824</v>
+        <v>9348</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3455</v>
+        <v>1379</v>
       </c>
       <c r="C4" t="n">
-        <v>6821</v>
+        <v>9362</v>
       </c>
       <c r="D4" t="n">
-        <v>7327</v>
+        <v>7407</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1684</v>
+        <v>727</v>
       </c>
       <c r="C5" t="n">
-        <v>7829</v>
+        <v>13207</v>
       </c>
       <c r="D5" t="n">
-        <v>3348</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>830</v>
+        <v>243</v>
       </c>
       <c r="C6" t="n">
-        <v>5686</v>
+        <v>8714</v>
       </c>
       <c r="D6" t="n">
-        <v>1109</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>152</v>
+        <v>60</v>
       </c>
       <c r="C7" t="n">
-        <v>3171</v>
+        <v>2870</v>
       </c>
       <c r="D7" t="n">
-        <v>567</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>1333</v>
+        <v>784</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>323</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
+        <v>63</v>
+      </c>
+      <c r="D13" t="n">
         <v>52</v>
-      </c>
-      <c r="D13" t="n">
-        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3949</v>
+        <v>285</v>
       </c>
       <c r="C2" t="n">
-        <v>12537</v>
+        <v>2514</v>
       </c>
       <c r="D2" t="n">
-        <v>11575</v>
+        <v>8104</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3313</v>
+        <v>647</v>
       </c>
       <c r="C3" t="n">
-        <v>4098</v>
+        <v>4107</v>
       </c>
       <c r="D3" t="n">
-        <v>9127</v>
+        <v>8824</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3344</v>
+        <v>973</v>
       </c>
       <c r="C4" t="n">
-        <v>6090</v>
+        <v>6949</v>
       </c>
       <c r="D4" t="n">
-        <v>7511</v>
+        <v>7184</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2131</v>
+        <v>683</v>
       </c>
       <c r="C5" t="n">
-        <v>7276</v>
+        <v>10112</v>
       </c>
       <c r="D5" t="n">
-        <v>3857</v>
+        <v>3633</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1065</v>
+        <v>239</v>
       </c>
       <c r="C6" t="n">
-        <v>6614</v>
+        <v>8660</v>
       </c>
       <c r="D6" t="n">
-        <v>1427</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>324</v>
+        <v>49</v>
       </c>
       <c r="C7" t="n">
-        <v>4267</v>
+        <v>3668</v>
       </c>
       <c r="D7" t="n">
-        <v>630</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>2043</v>
+        <v>943</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>668</v>
+        <v>254</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>110</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>69</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2691</v>
+        <v>329</v>
       </c>
       <c r="C2" t="n">
-        <v>5875</v>
+        <v>6811</v>
       </c>
       <c r="D2" t="n">
-        <v>8643</v>
+        <v>12372</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3084</v>
+        <v>405</v>
       </c>
       <c r="C3" t="n">
-        <v>6856</v>
+        <v>2919</v>
       </c>
       <c r="D3" t="n">
-        <v>8924</v>
+        <v>8178</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3068</v>
+        <v>728</v>
       </c>
       <c r="C4" t="n">
-        <v>5257</v>
+        <v>5331</v>
       </c>
       <c r="D4" t="n">
-        <v>7571</v>
+        <v>7180</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2348</v>
+        <v>733</v>
       </c>
       <c r="C5" t="n">
-        <v>6960</v>
+        <v>8322</v>
       </c>
       <c r="D5" t="n">
-        <v>4234</v>
+        <v>4136</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1270</v>
+        <v>385</v>
       </c>
       <c r="C6" t="n">
-        <v>7101</v>
+        <v>9351</v>
       </c>
       <c r="D6" t="n">
-        <v>1647</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>305</v>
+        <v>112</v>
       </c>
       <c r="C7" t="n">
-        <v>5156</v>
+        <v>5965</v>
       </c>
       <c r="D7" t="n">
-        <v>696</v>
+        <v>647</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>2619</v>
+        <v>2153</v>
       </c>
       <c r="D8" t="n">
-        <v>424</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>796</v>
+        <v>539</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>238</v>
+        <v>166</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3677</v>
+        <v>341</v>
       </c>
       <c r="C2" t="n">
-        <v>6025</v>
+        <v>14135</v>
       </c>
       <c r="D2" t="n">
-        <v>9251</v>
+        <v>12175</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2473</v>
+        <v>311</v>
       </c>
       <c r="C3" t="n">
-        <v>5781</v>
+        <v>4099</v>
       </c>
       <c r="D3" t="n">
-        <v>8319</v>
+        <v>8198</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2697</v>
+        <v>519</v>
       </c>
       <c r="C4" t="n">
-        <v>5838</v>
+        <v>4034</v>
       </c>
       <c r="D4" t="n">
-        <v>7535</v>
+        <v>7124</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2364</v>
+        <v>661</v>
       </c>
       <c r="C5" t="n">
-        <v>6112</v>
+        <v>6770</v>
       </c>
       <c r="D5" t="n">
-        <v>4513</v>
+        <v>4477</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1527</v>
+        <v>485</v>
       </c>
       <c r="C6" t="n">
-        <v>6984</v>
+        <v>8806</v>
       </c>
       <c r="D6" t="n">
-        <v>1973</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>548</v>
+        <v>196</v>
       </c>
       <c r="C7" t="n">
-        <v>5897</v>
+        <v>7422</v>
       </c>
       <c r="D7" t="n">
-        <v>810</v>
+        <v>799</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>3563</v>
+        <v>3721</v>
       </c>
       <c r="D8" t="n">
-        <v>451</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>1410</v>
+        <v>1166</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>409</v>
+        <v>308</v>
       </c>
       <c r="D10" t="n">
-        <v>191</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5326</v>
+        <v>7189</v>
       </c>
       <c r="C2" t="n">
-        <v>8027</v>
+        <v>28010</v>
       </c>
       <c r="D2" t="n">
-        <v>6406</v>
+        <v>8686</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2602</v>
+        <v>326</v>
       </c>
       <c r="C2" t="n">
-        <v>3423</v>
+        <v>13924</v>
       </c>
       <c r="D2" t="n">
-        <v>6808</v>
+        <v>11875</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3310</v>
+        <v>267</v>
       </c>
       <c r="C3" t="n">
-        <v>6337</v>
+        <v>7179</v>
       </c>
       <c r="D3" t="n">
-        <v>9084</v>
+        <v>8150</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3566</v>
+        <v>385</v>
       </c>
       <c r="C4" t="n">
-        <v>8092</v>
+        <v>3977</v>
       </c>
       <c r="D4" t="n">
-        <v>7767</v>
+        <v>7062</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1476</v>
+        <v>557</v>
       </c>
       <c r="C5" t="n">
-        <v>9396</v>
+        <v>5461</v>
       </c>
       <c r="D5" t="n">
-        <v>4259</v>
+        <v>4653</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C6" t="n">
-        <v>7216</v>
+        <v>7842</v>
       </c>
       <c r="D6" t="n">
-        <v>1657</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>105</v>
+        <v>272</v>
       </c>
       <c r="C7" t="n">
-        <v>3491</v>
+        <v>7961</v>
       </c>
       <c r="D7" t="n">
-        <v>545</v>
+        <v>940</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="C8" t="n">
-        <v>1381</v>
+        <v>5061</v>
       </c>
       <c r="D8" t="n">
-        <v>301</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>400</v>
+        <v>2091</v>
       </c>
       <c r="D9" t="n">
-        <v>187</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>162</v>
+        <v>602</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
         <v>37</v>
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6788</v>
+        <v>5756</v>
       </c>
       <c r="C2" t="n">
-        <v>8893</v>
+        <v>16003</v>
       </c>
       <c r="D2" t="n">
-        <v>12436</v>
+        <v>15183</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2263</v>
+        <v>2316</v>
       </c>
       <c r="C3" t="n">
-        <v>4045</v>
+        <v>10840</v>
       </c>
       <c r="D3" t="n">
-        <v>1715</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>208</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>168</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4225</v>
+        <v>3323</v>
       </c>
       <c r="C2" t="n">
-        <v>4971</v>
+        <v>8469</v>
       </c>
       <c r="D2" t="n">
-        <v>11448</v>
+        <v>23216</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3714</v>
+        <v>3367</v>
       </c>
       <c r="C3" t="n">
-        <v>5854</v>
+        <v>11939</v>
       </c>
       <c r="D3" t="n">
-        <v>3389</v>
+        <v>4023</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1016</v>
+        <v>1075</v>
       </c>
       <c r="C4" t="n">
-        <v>2412</v>
+        <v>6708</v>
       </c>
       <c r="D4" t="n">
-        <v>1526</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>136</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>754</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>190</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5557</v>
+        <v>3661</v>
       </c>
       <c r="C2" t="n">
-        <v>7533</v>
+        <v>5952</v>
       </c>
       <c r="D2" t="n">
-        <v>16420</v>
+        <v>20204</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3270</v>
+        <v>2763</v>
       </c>
       <c r="C3" t="n">
-        <v>4650</v>
+        <v>8649</v>
       </c>
       <c r="D3" t="n">
-        <v>4434</v>
+        <v>6804</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2000</v>
+        <v>1910</v>
       </c>
       <c r="C4" t="n">
-        <v>4311</v>
+        <v>9581</v>
       </c>
       <c r="D4" t="n">
-        <v>1837</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="C5" t="n">
-        <v>1414</v>
+        <v>3823</v>
       </c>
       <c r="D5" t="n">
-        <v>1200</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>797</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>215</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4760</v>
+        <v>2472</v>
       </c>
       <c r="C2" t="n">
-        <v>7333</v>
+        <v>9515</v>
       </c>
       <c r="D2" t="n">
-        <v>17244</v>
+        <v>24630</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3566</v>
+        <v>2624</v>
       </c>
       <c r="C3" t="n">
-        <v>5338</v>
+        <v>6319</v>
       </c>
       <c r="D3" t="n">
-        <v>5943</v>
+        <v>8361</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2246</v>
+        <v>2001</v>
       </c>
       <c r="C4" t="n">
-        <v>4362</v>
+        <v>8880</v>
       </c>
       <c r="D4" t="n">
-        <v>2254</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1013</v>
+        <v>984</v>
       </c>
       <c r="C5" t="n">
-        <v>2914</v>
+        <v>6691</v>
       </c>
       <c r="D5" t="n">
-        <v>1262</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="C6" t="n">
-        <v>863</v>
+        <v>2072</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>838</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>298</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>305</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>246</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5454</v>
+        <v>1795</v>
       </c>
       <c r="C2" t="n">
-        <v>8024</v>
+        <v>6533</v>
       </c>
       <c r="D2" t="n">
-        <v>19070</v>
+        <v>19314</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3020</v>
+        <v>2144</v>
       </c>
       <c r="C3" t="n">
-        <v>5208</v>
+        <v>6870</v>
       </c>
       <c r="D3" t="n">
-        <v>6813</v>
+        <v>10128</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1791</v>
+        <v>1950</v>
       </c>
       <c r="C4" t="n">
-        <v>3981</v>
+        <v>7416</v>
       </c>
       <c r="D4" t="n">
-        <v>2492</v>
+        <v>3628</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>849</v>
+        <v>1261</v>
       </c>
       <c r="C5" t="n">
-        <v>2687</v>
+        <v>7538</v>
       </c>
       <c r="D5" t="n">
-        <v>1120</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>307</v>
+        <v>509</v>
       </c>
       <c r="C6" t="n">
-        <v>1277</v>
+        <v>4223</v>
       </c>
       <c r="D6" t="n">
-        <v>761</v>
+        <v>884</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>153</v>
       </c>
       <c r="C7" t="n">
-        <v>383</v>
+        <v>1114</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>298</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>271</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4752</v>
+        <v>1325</v>
       </c>
       <c r="C2" t="n">
-        <v>7342</v>
+        <v>16900</v>
       </c>
       <c r="D2" t="n">
-        <v>16362</v>
+        <v>19516</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3521</v>
+        <v>1670</v>
       </c>
       <c r="C3" t="n">
-        <v>5908</v>
+        <v>5938</v>
       </c>
       <c r="D3" t="n">
-        <v>8457</v>
+        <v>10639</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2096</v>
+        <v>1744</v>
       </c>
       <c r="C4" t="n">
-        <v>4652</v>
+        <v>6938</v>
       </c>
       <c r="D4" t="n">
-        <v>3328</v>
+        <v>4481</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1185</v>
+        <v>1381</v>
       </c>
       <c r="C5" t="n">
-        <v>3401</v>
+        <v>7326</v>
       </c>
       <c r="D5" t="n">
-        <v>1362</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>539</v>
+        <v>732</v>
       </c>
       <c r="C6" t="n">
-        <v>2073</v>
+        <v>5615</v>
       </c>
       <c r="D6" t="n">
-        <v>811</v>
+        <v>937</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="C7" t="n">
-        <v>890</v>
+        <v>2412</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>638</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>310</v>
+        <v>633</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4329</v>
+        <v>1387</v>
       </c>
       <c r="C2" t="n">
-        <v>7338</v>
+        <v>11086</v>
       </c>
       <c r="D2" t="n">
-        <v>15369</v>
+        <v>15865</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3400</v>
+        <v>2581</v>
       </c>
       <c r="C3" t="n">
-        <v>5849</v>
+        <v>10798</v>
       </c>
       <c r="D3" t="n">
-        <v>9112</v>
+        <v>11294</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2428</v>
+        <v>1276</v>
       </c>
       <c r="C4" t="n">
-        <v>5221</v>
+        <v>11029</v>
       </c>
       <c r="D4" t="n">
-        <v>4179</v>
+        <v>4124</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1448</v>
+        <v>676</v>
       </c>
       <c r="C5" t="n">
-        <v>4026</v>
+        <v>5502</v>
       </c>
       <c r="D5" t="n">
-        <v>1698</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>777</v>
+        <v>241</v>
       </c>
       <c r="C6" t="n">
-        <v>2762</v>
+        <v>2363</v>
       </c>
       <c r="D6" t="n">
-        <v>900</v>
+        <v>625</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>318</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>1515</v>
+        <v>620</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>441</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>602</v>
+        <v>272</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>260</v>
+        <v>229</v>
       </c>
       <c r="D9" t="n">
         <v>295</v>
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,10 +6518,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
         <v>155</v>
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>142</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
